--- a/word-monitor-sub-domain/report/history/keyword-table-20260711-160824.xlsx
+++ b/word-monitor-sub-domain/report/history/keyword-table-20260711-160824.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="keywords" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>197</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">
@@ -637,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
@@ -1269,12 +1269,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>mangapiracy</t>
+          <t>study panda.in</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>https://piracy.vercel.app/type/comics-and-manga</t>
+          <t>https://studyreps.vercel.app/</t>
         </is>
       </c>
       <c r="C27" s="3" t="n"/>
@@ -1291,13 +1291,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>docx в markdown</t>
+          <t>verity mod</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>https://word2markdown.vercel.app/ru
-https://markdownvisualizer.vercel.app/word-to-markdown</t>
+          <t>https://verity-mod.vercel.app/</t>
         </is>
       </c>
       <c r="C28" s="3" t="n"/>
@@ -1314,12 +1313,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>лучшие масла для смазки электробритвы</t>
+          <t>averis.co.uk</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>https://maslo-wiki.vercel.app/articles/m/ma/maslo-dlya-britvennoj-mashinki.html</t>
+          <t>https://averis-inky.vercel.app/faq</t>
         </is>
       </c>
       <c r="C29" s="3" t="n"/>
@@ -1333,8 +1332,911 @@
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>piratebay proxy</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>https://proxybay.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="7" t="n"/>
+      <c r="I30" s="7" t="n"/>
+      <c r="J30" s="8" t="n"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>burn cd</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>https://burn-cd.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="7" t="n"/>
+      <c r="I31" s="7" t="n"/>
+      <c r="J31" s="8" t="n"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>thespinearchive</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>https://thespinearchive.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="7" t="n"/>
+      <c r="I32" s="7" t="n"/>
+      <c r="J32" s="8" t="n"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>bad piggies unity mod</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>https://badpig.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="7" t="n"/>
+      <c r="I33" s="7" t="n"/>
+      <c r="J33" s="8" t="n"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>anymex</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>https://anymex.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="7" t="n"/>
+      <c r="I34" s="7" t="n"/>
+      <c r="J34" s="8" t="n"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>codashop</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>https://codashopbysdr.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="6" t="n"/>
+      <c r="H35" s="7" t="n"/>
+      <c r="I35" s="7" t="n"/>
+      <c r="J35" s="8" t="n"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>butterstream</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>https://butterstream.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="7" t="n"/>
+      <c r="I36" s="7" t="n"/>
+      <c r="J36" s="8" t="n"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>ワールドカップ 速報 リアルタイム</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>https://worldcup-chi-six.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="7" t="n"/>
+      <c r="I37" s="7" t="n"/>
+      <c r="J37" s="8" t="n"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>ipu result</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>https://ipuresult.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="6" t="n"/>
+      <c r="H38" s="7" t="n"/>
+      <c r="I38" s="7" t="n"/>
+      <c r="J38" s="8" t="n"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>orkut</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>https://orkut-login.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="6" t="n"/>
+      <c r="H39" s="7" t="n"/>
+      <c r="I39" s="7" t="n"/>
+      <c r="J39" s="8" t="n"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>movix</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>https://movix-app-murex.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="7" t="n"/>
+      <c r="I40" s="7" t="n"/>
+      <c r="J40" s="8" t="n"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>youtube 2</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube-2.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="6" t="n"/>
+      <c r="H41" s="7" t="n"/>
+      <c r="I41" s="7" t="n"/>
+      <c r="J41" s="8" t="n"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>deltarune prophecy maker</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>https://deltaprophecy.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n"/>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="6" t="n"/>
+      <c r="H42" s="7" t="n"/>
+      <c r="I42" s="7" t="n"/>
+      <c r="J42" s="8" t="n"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>vega app</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>https://vegaapp.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="6" t="n"/>
+      <c r="H43" s="7" t="n"/>
+      <c r="I43" s="7" t="n"/>
+      <c r="J43" s="8" t="n"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>lkz</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>https://lkzstream.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="6" t="n"/>
+      <c r="H44" s="7" t="n"/>
+      <c r="I44" s="7" t="n"/>
+      <c r="J44" s="8" t="n"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>reanime</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>https://reanimeweb.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="6" t="n"/>
+      <c r="H45" s="7" t="n"/>
+      <c r="I45" s="7" t="n"/>
+      <c r="J45" s="8" t="n"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>варп генератор</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>https://warp-generator.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="6" t="n"/>
+      <c r="H46" s="7" t="n"/>
+      <c r="I46" s="7" t="n"/>
+      <c r="J46" s="8" t="n"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>hiphopkit</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>https://hiphopkit.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="6" t="n"/>
+      <c r="H47" s="7" t="n"/>
+      <c r="I47" s="7" t="n"/>
+      <c r="J47" s="8" t="n"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>w101 pet calculator</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>https://petbodyw101.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="6" t="n"/>
+      <c r="H48" s="7" t="n"/>
+      <c r="I48" s="7" t="n"/>
+      <c r="J48" s="8" t="n"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>trustified</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>https://trustified-simplified-frontend.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n"/>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="n"/>
+      <c r="G49" s="6" t="n"/>
+      <c r="H49" s="7" t="n"/>
+      <c r="I49" s="7" t="n"/>
+      <c r="J49" s="8" t="n"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>курсоры для роблокс</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>https://cursor-x.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n"/>
+      <c r="D50" s="4" t="n"/>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="n"/>
+      <c r="G50" s="6" t="n"/>
+      <c r="H50" s="7" t="n"/>
+      <c r="I50" s="7" t="n"/>
+      <c r="J50" s="8" t="n"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>iit m mess menu</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>https://mess-menu-iitm.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="6" t="n"/>
+      <c r="H51" s="7" t="n"/>
+      <c r="I51" s="7" t="n"/>
+      <c r="J51" s="8" t="n"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>spidey universe</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>https://spidyuniverserwa.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="6" t="n"/>
+      <c r="H52" s="7" t="n"/>
+      <c r="I52" s="7" t="n"/>
+      <c r="J52" s="8" t="n"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>dataenrich.co</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>https://data-enrich.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="n"/>
+      <c r="G53" s="6" t="n"/>
+      <c r="H53" s="7" t="n"/>
+      <c r="I53" s="7" t="n"/>
+      <c r="J53" s="8" t="n"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>fitgirl link extractor</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>https://fitgirl-download-link-extractor.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="n"/>
+      <c r="G54" s="6" t="n"/>
+      <c r="H54" s="7" t="n"/>
+      <c r="I54" s="7" t="n"/>
+      <c r="J54" s="8" t="n"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>shonenx</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>https://shonenx.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="n"/>
+      <c r="G55" s="6" t="n"/>
+      <c r="H55" s="7" t="n"/>
+      <c r="I55" s="7" t="n"/>
+      <c r="J55" s="8" t="n"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>supermium</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>https://supermium.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n"/>
+      <c r="D56" s="4" t="n"/>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="n"/>
+      <c r="G56" s="6" t="n"/>
+      <c r="H56" s="7" t="n"/>
+      <c r="I56" s="7" t="n"/>
+      <c r="J56" s="8" t="n"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>epson l805ni reset qiladigan dastur</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>https://printer-e.vercel.app/articles/e/ep/epson-l805-kak-sbrosit-nastrojki.html</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n"/>
+      <c r="D57" s="4" t="n"/>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="6" t="n"/>
+      <c r="H57" s="7" t="n"/>
+      <c r="I57" s="7" t="n"/>
+      <c r="J57" s="8" t="n"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>מפת גיוס</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>https://recruitment-data.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="6" t="n"/>
+      <c r="H58" s="7" t="n"/>
+      <c r="I58" s="7" t="n"/>
+      <c r="J58" s="8" t="n"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>zanime</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>https://zanime.vercel.app/home</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n"/>
+      <c r="D59" s="4" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="n"/>
+      <c r="G59" s="6" t="n"/>
+      <c r="H59" s="7" t="n"/>
+      <c r="I59" s="7" t="n"/>
+      <c r="J59" s="8" t="n"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>acpc</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>https://acpc-master.vercel.app/recommendations</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n"/>
+      <c r="D60" s="4" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="6" t="n"/>
+      <c r="H60" s="7" t="n"/>
+      <c r="I60" s="7" t="n"/>
+      <c r="J60" s="8" t="n"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>bate papo uol</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>https://bate-papo-uol-gamma.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n"/>
+      <c r="D61" s="4" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="n"/>
+      <c r="G61" s="6" t="n"/>
+      <c r="H61" s="7" t="n"/>
+      <c r="I61" s="7" t="n"/>
+      <c r="J61" s="8" t="n"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>cfx username availabilty</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>https://cfx-id.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n"/>
+      <c r="D62" s="4" t="n"/>
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="5" t="n"/>
+      <c r="G62" s="6" t="n"/>
+      <c r="H62" s="7" t="n"/>
+      <c r="I62" s="7" t="n"/>
+      <c r="J62" s="8" t="n"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>criterion closet</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>https://the-criterion-closet.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="n"/>
+      <c r="D63" s="4" t="n"/>
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="5" t="n"/>
+      <c r="G63" s="6" t="n"/>
+      <c r="H63" s="7" t="n"/>
+      <c r="I63" s="7" t="n"/>
+      <c r="J63" s="8" t="n"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>snbt generator</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>https://fake-pengumuman-snbt-2023.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n"/>
+      <c r="D64" s="4" t="n"/>
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="5" t="n"/>
+      <c r="G64" s="6" t="n"/>
+      <c r="H64" s="7" t="n"/>
+      <c r="I64" s="7" t="n"/>
+      <c r="J64" s="8" t="n"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>gacha revenue</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>https://gacharevenue.vercel.app/revenue</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="n"/>
+      <c r="D65" s="4" t="n"/>
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" s="5" t="n"/>
+      <c r="G65" s="6" t="n"/>
+      <c r="H65" s="7" t="n"/>
+      <c r="I65" s="7" t="n"/>
+      <c r="J65" s="8" t="n"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>نتيجه الثانويه العامه</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>https://nategaeg.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="n"/>
+      <c r="G66" s="6" t="n"/>
+      <c r="H66" s="7" t="n"/>
+      <c r="I66" s="7" t="n"/>
+      <c r="J66" s="8" t="n"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>iuh</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>https://sv-iuh.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" s="5" t="n"/>
+      <c r="G67" s="6" t="n"/>
+      <c r="H67" s="7" t="n"/>
+      <c r="I67" s="7" t="n"/>
+      <c r="J67" s="8" t="n"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>mangapiracy</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>https://piracy.vercel.app/type/comics-and-manga</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n"/>
+      <c r="D68" s="4" t="n"/>
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="5" t="n"/>
+      <c r="G68" s="6" t="n"/>
+      <c r="H68" s="7" t="n"/>
+      <c r="I68" s="7" t="n"/>
+      <c r="J68" s="8" t="n"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>docx в markdown</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>https://word2markdown.vercel.app/ru
+https://markdownvisualizer.vercel.app/word-to-markdown</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="n"/>
+      <c r="D69" s="4" t="n"/>
+      <c r="E69" s="5" t="n"/>
+      <c r="F69" s="5" t="n"/>
+      <c r="G69" s="6" t="n"/>
+      <c r="H69" s="7" t="n"/>
+      <c r="I69" s="7" t="n"/>
+      <c r="J69" s="8" t="n"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>лучшие масла для смазки электробритвы</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>https://maslo-wiki.vercel.app/articles/m/ma/maslo-dlya-britvennoj-mashinki.html</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n"/>
+      <c r="D70" s="4" t="n"/>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="5" t="n"/>
+      <c r="G70" s="6" t="n"/>
+      <c r="H70" s="7" t="n"/>
+      <c r="I70" s="7" t="n"/>
+      <c r="J70" s="8" t="n"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L29"/>
+  <autoFilter ref="A1:L70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>